--- a/output/yearly_benthic_cover_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_7_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.13532717798718</v>
+        <v>45.73736355240379</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6824307789021</v>
+        <v>98.45608201176293</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06876279665497</v>
+        <v>87.91707295887181</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9180654037973</v>
+        <v>45.91615188207403</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228844959902077</v>
+        <v>2.228457029239338</v>
       </c>
       <c r="E3" t="n">
-        <v>5.702663018904592</v>
+        <v>5.693009041228669</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742948319967359</v>
+        <v>0.7428190097464461</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96898063610411</v>
+        <v>33.9699530102976</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17562271849851</v>
+        <v>34.16967444833652</v>
       </c>
       <c r="I3" t="n">
-        <v>6.606276143482319</v>
+        <v>6.470541609107937</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643426999795993</v>
+        <v>4.642618810915287</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93123720334503</v>
+        <v>12.08292704112821</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91357812212032</v>
+        <v>48.76863330012687</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7628807292627</v>
+        <v>106.7677122233291</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.28916786415891</v>
+        <v>86.86338222813585</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78138035564351</v>
+        <v>42.47923369437443</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191983564600287</v>
+        <v>2.176909319109711</v>
       </c>
       <c r="E4" t="n">
-        <v>6.527821794384725</v>
+        <v>6.461870550683463</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445135077554932</v>
+        <v>0.7443592340723559</v>
       </c>
       <c r="G4" t="n">
-        <v>33.407190091785</v>
+        <v>33.18417465876727</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24762135675268</v>
+        <v>34.24052476732837</v>
       </c>
       <c r="I4" t="n">
-        <v>5.516828125408892</v>
+        <v>5.403298485222448</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653209423471832</v>
+        <v>4.652245212952224</v>
       </c>
       <c r="K4" t="n">
-        <v>12.71083213584109</v>
+        <v>13.13661777186416</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3242798378631</v>
+        <v>44.20441126684175</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81649232934771</v>
+        <v>99.82026273308034</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.25978211112351</v>
+        <v>85.525076712859</v>
       </c>
       <c r="C5" t="n">
-        <v>42.60834933401911</v>
+        <v>41.97946637030351</v>
       </c>
       <c r="D5" t="n">
-        <v>2.14222757416178</v>
+        <v>2.110954336193873</v>
       </c>
       <c r="E5" t="n">
-        <v>7.147236098195291</v>
+        <v>7.017869260948267</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458385307405523</v>
+        <v>0.7456678385377578</v>
       </c>
       <c r="G5" t="n">
-        <v>32.64887791388902</v>
+        <v>32.17877601699459</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3085724140654</v>
+        <v>34.30072057273685</v>
       </c>
       <c r="I5" t="n">
-        <v>4.605538762943019</v>
+        <v>4.51066469658667</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661490817128452</v>
+        <v>4.660423990860985</v>
       </c>
       <c r="K5" t="n">
-        <v>13.74021788887649</v>
+        <v>14.474923287141</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49818755139859</v>
+        <v>43.39551871796596</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84675477429418</v>
+        <v>99.84990837541049</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.04622759473483</v>
+        <v>83.98172170726087</v>
       </c>
       <c r="C6" t="n">
-        <v>42.11028376211782</v>
+        <v>41.13639365493562</v>
       </c>
       <c r="D6" t="n">
-        <v>2.083372649048773</v>
+        <v>2.035120104719204</v>
       </c>
       <c r="E6" t="n">
-        <v>7.591496876344427</v>
+        <v>7.393175582919008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469621559804541</v>
+        <v>0.7467819973766415</v>
       </c>
       <c r="G6" t="n">
-        <v>31.75189232383212</v>
+        <v>31.02278097380283</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36025917510089</v>
+        <v>34.3519718793255</v>
       </c>
       <c r="I6" t="n">
-        <v>3.843730939550337</v>
+        <v>3.764503685513687</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668513474877838</v>
+        <v>4.667387483604008</v>
       </c>
       <c r="K6" t="n">
-        <v>14.95377240526517</v>
+        <v>16.01827829273913</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80801220031304</v>
+        <v>42.72003181075339</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87206836769602</v>
+        <v>99.87470375842814</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.58281293487686</v>
+        <v>82.17382613793671</v>
       </c>
       <c r="C7" t="n">
-        <v>41.24416086472979</v>
+        <v>39.91281082359266</v>
       </c>
       <c r="D7" t="n">
-        <v>2.012347402733575</v>
+        <v>1.946640876975643</v>
       </c>
       <c r="E7" t="n">
-        <v>7.867225895243997</v>
+        <v>7.595262551004397</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479175603559435</v>
+        <v>0.7477335187901706</v>
       </c>
       <c r="G7" t="n">
-        <v>30.66942348451838</v>
+        <v>29.67402927278298</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4042077763734</v>
+        <v>34.39574186434784</v>
       </c>
       <c r="I7" t="n">
-        <v>3.207206063426918</v>
+        <v>3.141083561597116</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674484752224647</v>
+        <v>4.673334492438565</v>
       </c>
       <c r="K7" t="n">
-        <v>16.41718706512314</v>
+        <v>17.82617386206327</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23188176627067</v>
+        <v>42.15644576752425</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89322969612361</v>
+        <v>99.8954304531802</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.38516233851429</v>
+        <v>87.27147429179823</v>
       </c>
       <c r="C8" t="n">
-        <v>43.47301945555169</v>
+        <v>42.22341710090976</v>
       </c>
       <c r="D8" t="n">
-        <v>2.016640918116722</v>
+        <v>1.950952490727708</v>
       </c>
       <c r="E8" t="n">
-        <v>9.652138819502335</v>
+        <v>9.444085191672432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495133064713271</v>
+        <v>0.749389673328292</v>
       </c>
       <c r="G8" t="n">
-        <v>31.14747981851753</v>
+        <v>30.17251036728719</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47761209768104</v>
+        <v>34.47192497310142</v>
       </c>
       <c r="I8" t="n">
-        <v>5.657319212779537</v>
+        <v>5.798926137379368</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684458165445794</v>
+        <v>4.683685458301824</v>
       </c>
       <c r="K8" t="n">
-        <v>11.61483766148571</v>
+        <v>12.72852570820175</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72396706507986</v>
+        <v>44.85518684140131</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81182418211726</v>
+        <v>99.80712965051282</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.57865880957866</v>
+        <v>85.24321094589459</v>
       </c>
       <c r="C9" t="n">
-        <v>42.54500811322499</v>
+        <v>41.09408078508132</v>
       </c>
       <c r="D9" t="n">
-        <v>1.935067123175869</v>
+        <v>1.859270346664415</v>
       </c>
       <c r="E9" t="n">
-        <v>10.04887415518002</v>
+        <v>9.80720553182568</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508762117561457</v>
+        <v>0.750808451272253</v>
       </c>
       <c r="G9" t="n">
-        <v>29.88755391459761</v>
+        <v>28.75459760139866</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5403057407827</v>
+        <v>34.53718875852363</v>
       </c>
       <c r="I9" t="n">
-        <v>4.723005340610394</v>
+        <v>4.841587435758369</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692976323475911</v>
+        <v>4.692552820451581</v>
       </c>
       <c r="K9" t="n">
-        <v>13.42134119042135</v>
+        <v>14.75678905410541</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87650294044312</v>
+        <v>43.98804887921938</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84285224408946</v>
+        <v>99.83891871840612</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.58714286419212</v>
+        <v>83.07118731840838</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28682842329678</v>
+        <v>39.6723010030857</v>
       </c>
       <c r="D10" t="n">
-        <v>1.845893335681632</v>
+        <v>1.762215529543908</v>
       </c>
       <c r="E10" t="n">
-        <v>10.24278338196193</v>
+        <v>9.968797748707939</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520426292892725</v>
+        <v>0.7520259476740864</v>
       </c>
       <c r="G10" t="n">
-        <v>28.51024438895762</v>
+        <v>27.25359360992199</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59396094730653</v>
+        <v>34.59319359300797</v>
       </c>
       <c r="I10" t="n">
-        <v>3.941951747937193</v>
+        <v>4.041198716589458</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700266433057953</v>
+        <v>4.700162172963039</v>
       </c>
       <c r="K10" t="n">
-        <v>15.41285713580788</v>
+        <v>16.92881268159161</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16911984810061</v>
+        <v>43.26439777544052</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86880540720527</v>
+        <v>99.86551146011783</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.44620206596035</v>
+        <v>80.78644794657056</v>
       </c>
       <c r="C11" t="n">
-        <v>39.75751623598328</v>
+        <v>38.01317106353639</v>
       </c>
       <c r="D11" t="n">
-        <v>1.750877499493715</v>
+        <v>1.661247146642864</v>
       </c>
       <c r="E11" t="n">
-        <v>10.2637659634451</v>
+        <v>9.959681385775818</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530427623588674</v>
+        <v>0.7530723673679078</v>
       </c>
       <c r="G11" t="n">
-        <v>27.04270308623205</v>
+        <v>25.69206425729607</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63996706850789</v>
+        <v>34.64132889892375</v>
       </c>
       <c r="I11" t="n">
-        <v>3.289328421179805</v>
+        <v>3.372351594514715</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706517264742922</v>
+        <v>4.706702296049423</v>
       </c>
       <c r="K11" t="n">
-        <v>17.55379793403965</v>
+        <v>19.21355205342945</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57918717031215</v>
+        <v>42.66102136312889</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89050134033508</v>
+        <v>99.88774448009474</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.17163670762032</v>
+        <v>78.3827499052237</v>
       </c>
       <c r="C12" t="n">
-        <v>37.99267512279802</v>
+        <v>36.13074928164061</v>
       </c>
       <c r="D12" t="n">
-        <v>1.650793804825213</v>
+        <v>1.556089532622747</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1344407971119</v>
+        <v>9.798172145820715</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539019714546854</v>
+        <v>0.7539734526684941</v>
       </c>
       <c r="G12" t="n">
-        <v>25.49688755117833</v>
+        <v>24.0657462335098</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67949068691552</v>
+        <v>34.68277882275073</v>
       </c>
       <c r="I12" t="n">
-        <v>2.744234574542885</v>
+        <v>2.813655638673128</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711887321591784</v>
+        <v>4.712334079178087</v>
       </c>
       <c r="K12" t="n">
-        <v>19.82836329237967</v>
+        <v>21.61725009477631</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08759135090065</v>
+        <v>42.15832419040211</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90862976607835</v>
+        <v>99.90632356681903</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.90340158134578</v>
+        <v>75.97620129782348</v>
       </c>
       <c r="C13" t="n">
-        <v>36.14893268920432</v>
+        <v>34.15821826259283</v>
       </c>
       <c r="D13" t="n">
-        <v>1.551878434682477</v>
+        <v>1.451857366536036</v>
       </c>
       <c r="E13" t="n">
-        <v>9.908703306055909</v>
+        <v>9.533045193591722</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546403895919155</v>
+        <v>0.7547498676600944</v>
       </c>
       <c r="G13" t="n">
-        <v>23.96911705540792</v>
+        <v>22.45374075064793</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71345792122811</v>
+        <v>34.71849391236434</v>
       </c>
       <c r="I13" t="n">
-        <v>2.289102039429984</v>
+        <v>2.347127534147772</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716502434949472</v>
+        <v>4.71718667287559</v>
       </c>
       <c r="K13" t="n">
-        <v>22.09659841865422</v>
+        <v>24.02379870217651</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67824015395971</v>
+        <v>41.73982593415642</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92377126181825</v>
+        <v>99.92184289892576</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.26824898517714</v>
+        <v>82.95692857661464</v>
       </c>
       <c r="C14" t="n">
-        <v>40.04032452919648</v>
+        <v>38.43709485229972</v>
       </c>
       <c r="D14" t="n">
-        <v>1.553735151771801</v>
+        <v>1.453678745399451</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10291086383258</v>
+        <v>11.92969435520028</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555432655365357</v>
+        <v>0.7556967137400238</v>
       </c>
       <c r="G14" t="n">
-        <v>25.67604077541774</v>
+        <v>24.34624500346669</v>
       </c>
       <c r="H14" t="n">
-        <v>36.43323651495307</v>
+        <v>36.62638449905352</v>
       </c>
       <c r="I14" t="n">
-        <v>3.024637004062068</v>
+        <v>3.122124798879538</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722145409603349</v>
+        <v>4.723104460875148</v>
       </c>
       <c r="K14" t="n">
-        <v>15.73175101482287</v>
+        <v>17.04307142338533</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12722370411842</v>
+        <v>44.4158932926608</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89929924813777</v>
+        <v>99.89605956834586</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.55985911170079</v>
+        <v>82.33019065970055</v>
       </c>
       <c r="C15" t="n">
-        <v>39.79992865586873</v>
+        <v>38.29028111968083</v>
       </c>
       <c r="D15" t="n">
-        <v>1.527287714310552</v>
+        <v>1.430816045869858</v>
       </c>
       <c r="E15" t="n">
-        <v>12.31740829056887</v>
+        <v>12.1780823173833</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563037131370748</v>
+        <v>0.7564935955116016</v>
       </c>
       <c r="G15" t="n">
-        <v>25.23898721330584</v>
+        <v>23.96526624142744</v>
       </c>
       <c r="H15" t="n">
-        <v>36.46990624460514</v>
+        <v>36.66693325608299</v>
       </c>
       <c r="I15" t="n">
-        <v>2.523067728666604</v>
+        <v>2.604514231477846</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726898207106718</v>
+        <v>4.728084971947509</v>
       </c>
       <c r="K15" t="n">
-        <v>16.44014088829919</v>
+        <v>17.66980934029945</v>
       </c>
       <c r="L15" t="n">
-        <v>43.67591276127481</v>
+        <v>43.95318385116195</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91598230544272</v>
+        <v>99.91327431114223</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.22544960306571</v>
+        <v>79.87249327436612</v>
       </c>
       <c r="C16" t="n">
-        <v>37.85600349611314</v>
+        <v>36.23469890256303</v>
       </c>
       <c r="D16" t="n">
-        <v>1.437305296364859</v>
+        <v>1.338439805931199</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94243863524765</v>
+        <v>11.75390790883281</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569568518236165</v>
+        <v>0.7571794402412051</v>
       </c>
       <c r="G16" t="n">
-        <v>23.75199489700943</v>
+        <v>22.41802249132953</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50140140488156</v>
+        <v>36.7001758678825</v>
       </c>
       <c r="I16" t="n">
-        <v>2.104372193841003</v>
+        <v>2.172396258641342</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730980323897604</v>
+        <v>4.732371501507531</v>
       </c>
       <c r="K16" t="n">
-        <v>18.7745503969343</v>
+        <v>20.12750672563388</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29936089226736</v>
+        <v>43.56544675426204</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92991478531479</v>
+        <v>99.92765238245894</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.78302178828439</v>
+        <v>81.87745770588714</v>
       </c>
       <c r="C17" t="n">
-        <v>38.99399959420567</v>
+        <v>37.66513767901998</v>
       </c>
       <c r="D17" t="n">
-        <v>1.438527172440303</v>
+        <v>1.339634467040939</v>
       </c>
       <c r="E17" t="n">
-        <v>12.68165077344306</v>
+        <v>12.64652184428245</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576003528736204</v>
+        <v>0.7578552814903539</v>
       </c>
       <c r="G17" t="n">
-        <v>24.14937071423295</v>
+        <v>22.95474513652043</v>
       </c>
       <c r="H17" t="n">
-        <v>36.90961569520295</v>
+        <v>37.24964644026946</v>
       </c>
       <c r="I17" t="n">
-        <v>2.111254874631361</v>
+        <v>2.192459026968785</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735002205460128</v>
+        <v>4.736595509314711</v>
       </c>
       <c r="K17" t="n">
-        <v>17.21697821171561</v>
+        <v>18.12254229411287</v>
       </c>
       <c r="L17" t="n">
-        <v>43.71870680781841</v>
+        <v>44.13930323244138</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9296846137397</v>
+        <v>99.92698320557423</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.52966537011189</v>
+        <v>79.53829653836347</v>
       </c>
       <c r="C18" t="n">
-        <v>37.06702243851625</v>
+        <v>35.66410376000063</v>
       </c>
       <c r="D18" t="n">
-        <v>1.354811631839034</v>
+        <v>1.25576804592603</v>
       </c>
       <c r="E18" t="n">
-        <v>12.23708166856575</v>
+        <v>12.15954104611053</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581524796758206</v>
+        <v>0.7584360079888748</v>
       </c>
       <c r="G18" t="n">
-        <v>22.74399050087702</v>
+        <v>21.5176872154465</v>
       </c>
       <c r="H18" t="n">
-        <v>36.93651482217264</v>
+        <v>37.27818995943034</v>
       </c>
       <c r="I18" t="n">
-        <v>1.760661269007755</v>
+        <v>1.828449213530731</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738452997973878</v>
+        <v>4.740225049930467</v>
       </c>
       <c r="K18" t="n">
-        <v>19.4703346298881</v>
+        <v>20.46170346163653</v>
       </c>
       <c r="L18" t="n">
-        <v>43.40399696285588</v>
+        <v>43.81329113872482</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94135403126023</v>
+        <v>99.93909836036198</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.57988337111537</v>
+        <v>78.66184127539712</v>
       </c>
       <c r="C19" t="n">
-        <v>36.38879056932327</v>
+        <v>35.06892833216263</v>
       </c>
       <c r="D19" t="n">
-        <v>1.320209631496026</v>
+        <v>1.225052304938757</v>
       </c>
       <c r="E19" t="n">
-        <v>12.16923226174238</v>
+        <v>12.11623737323691</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586187025280824</v>
+        <v>0.7589260301734633</v>
       </c>
       <c r="G19" t="n">
-        <v>22.16310711560194</v>
+        <v>20.99137050488916</v>
       </c>
       <c r="H19" t="n">
-        <v>36.95922878506882</v>
+        <v>37.30227523477198</v>
       </c>
       <c r="I19" t="n">
-        <v>1.468119983877596</v>
+        <v>1.524692138802724</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741366890800514</v>
+        <v>4.743287688584145</v>
       </c>
       <c r="K19" t="n">
-        <v>20.42011662888464</v>
+        <v>21.33815872460287</v>
       </c>
       <c r="L19" t="n">
-        <v>43.14218554431965</v>
+        <v>43.54212268730308</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95109274252756</v>
+        <v>99.94920974406858</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.07203831304801</v>
+        <v>76.10369146496417</v>
       </c>
       <c r="C20" t="n">
-        <v>34.10722820661741</v>
+        <v>32.74519919986126</v>
       </c>
       <c r="D20" t="n">
-        <v>1.227994196829049</v>
+        <v>1.134404134951555</v>
       </c>
       <c r="E20" t="n">
-        <v>11.52323602697631</v>
+        <v>11.43157289957621</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590203227843602</v>
+        <v>0.7593486162105237</v>
       </c>
       <c r="G20" t="n">
-        <v>20.61503436451918</v>
+        <v>19.43810676739784</v>
       </c>
       <c r="H20" t="n">
-        <v>36.97879536691952</v>
+        <v>37.32304592919815</v>
       </c>
       <c r="I20" t="n">
-        <v>1.224081017617337</v>
+        <v>1.271284266314122</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743877017402251</v>
+        <v>4.745928851315773</v>
       </c>
       <c r="K20" t="n">
-        <v>22.92796168695198</v>
+        <v>23.89630853503583</v>
       </c>
       <c r="L20" t="n">
-        <v>42.92402899576734</v>
+        <v>43.31613970569173</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95921888933674</v>
+        <v>99.95764744058881</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.60117266102677</v>
+        <v>82.04674046253041</v>
       </c>
       <c r="C21" t="n">
-        <v>37.48729338052775</v>
+        <v>36.40173262147562</v>
       </c>
       <c r="D21" t="n">
-        <v>1.228886943902558</v>
+        <v>1.135257099271265</v>
       </c>
       <c r="E21" t="n">
-        <v>13.36396653340753</v>
+        <v>13.41491470647632</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595721276492772</v>
+        <v>0.7599195743513599</v>
       </c>
       <c r="G21" t="n">
-        <v>22.16212089414637</v>
+        <v>21.11901189187511</v>
       </c>
       <c r="H21" t="n">
-        <v>38.53777828806406</v>
+        <v>39.01739883167199</v>
       </c>
       <c r="I21" t="n">
-        <v>1.801522076048978</v>
+        <v>1.850741019188356</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747325797807981</v>
+        <v>4.749497339695998</v>
       </c>
       <c r="K21" t="n">
-        <v>17.39882733897325</v>
+        <v>17.95325953746959</v>
       </c>
       <c r="L21" t="n">
-        <v>45.0538721695703</v>
+        <v>45.58336282495405</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93999288907129</v>
+        <v>99.93835498389926</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_7_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.73736355240379</v>
+        <v>45.23535751270754</v>
       </c>
       <c r="M2" t="n">
-        <v>98.45608201176293</v>
+        <v>100.7051283870477</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.91707295887181</v>
+        <v>88.03369476865926</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91615188207403</v>
+        <v>45.89828209672594</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228457029239338</v>
+        <v>2.22877005237442</v>
       </c>
       <c r="E3" t="n">
-        <v>5.693009041228669</v>
+        <v>5.689460331748026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428190097464461</v>
+        <v>0.7429233507914735</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9699530102976</v>
+        <v>33.962478178676</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16967444833652</v>
+        <v>34.17447413640778</v>
       </c>
       <c r="I3" t="n">
-        <v>6.470541609107937</v>
+        <v>6.592317776214852</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642618810915287</v>
+        <v>4.643270942446709</v>
       </c>
       <c r="K3" t="n">
-        <v>12.08292704112821</v>
+        <v>11.96630523134073</v>
       </c>
       <c r="L3" t="n">
-        <v>48.76863330012687</v>
+        <v>48.89878645670967</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7677122233291</v>
+        <v>106.7633737847763</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.86338222813585</v>
+        <v>87.19414353015281</v>
       </c>
       <c r="C4" t="n">
-        <v>42.47923369437443</v>
+        <v>42.69968036622443</v>
       </c>
       <c r="D4" t="n">
-        <v>2.176909319109711</v>
+        <v>2.188688118425159</v>
       </c>
       <c r="E4" t="n">
-        <v>6.461870550683463</v>
+        <v>6.504668383707318</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443592340723559</v>
+        <v>0.7444868777158694</v>
       </c>
       <c r="G4" t="n">
-        <v>33.18417465876727</v>
+        <v>33.35170103472584</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24052476732837</v>
+        <v>34.24639637492999</v>
       </c>
       <c r="I4" t="n">
-        <v>5.403298485222448</v>
+        <v>5.505159754924462</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652245212952224</v>
+        <v>4.653042985724183</v>
       </c>
       <c r="K4" t="n">
-        <v>13.13661777186416</v>
+        <v>12.80585646984717</v>
       </c>
       <c r="L4" t="n">
-        <v>44.20441126684175</v>
+        <v>44.31134322570021</v>
       </c>
       <c r="M4" t="n">
-        <v>99.82026273308034</v>
+        <v>99.81688006177181</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.525076712859</v>
+        <v>86.12163390237106</v>
       </c>
       <c r="C5" t="n">
-        <v>41.97946637030351</v>
+        <v>42.48164030830971</v>
       </c>
       <c r="D5" t="n">
-        <v>2.110954336193873</v>
+        <v>2.136651723344799</v>
       </c>
       <c r="E5" t="n">
-        <v>7.017869260948267</v>
+        <v>7.115984498534558</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456678385377578</v>
+        <v>0.7458111706100432</v>
       </c>
       <c r="G5" t="n">
-        <v>32.17877601699459</v>
+        <v>32.55875923683559</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30072057273685</v>
+        <v>34.30731384806198</v>
       </c>
       <c r="I5" t="n">
-        <v>4.51066469658667</v>
+        <v>4.595793608671321</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660423990860985</v>
+        <v>4.661319816312769</v>
       </c>
       <c r="K5" t="n">
-        <v>14.474923287141</v>
+        <v>13.87836609762894</v>
       </c>
       <c r="L5" t="n">
-        <v>43.39551871796596</v>
+        <v>43.48707248975789</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84990837541049</v>
+        <v>99.84707889569654</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.98172170726087</v>
+        <v>84.90920530396744</v>
       </c>
       <c r="C6" t="n">
-        <v>41.13639365493562</v>
+        <v>41.9830826987924</v>
       </c>
       <c r="D6" t="n">
-        <v>2.035120104719204</v>
+        <v>2.077818027156258</v>
       </c>
       <c r="E6" t="n">
-        <v>7.393175582919008</v>
+        <v>7.559308368530477</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7467819973766415</v>
+        <v>0.7469341856602785</v>
       </c>
       <c r="G6" t="n">
-        <v>31.02278097380283</v>
+        <v>31.66223870038749</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3519718793255</v>
+        <v>34.3589725403728</v>
       </c>
       <c r="I6" t="n">
-        <v>3.764503685513687</v>
+        <v>3.835594821483401</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667387483604008</v>
+        <v>4.668338660376739</v>
       </c>
       <c r="K6" t="n">
-        <v>16.01827829273913</v>
+        <v>15.09079469603254</v>
       </c>
       <c r="L6" t="n">
-        <v>42.72003181075339</v>
+        <v>42.79846167160085</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87470375842814</v>
+        <v>99.87233906642579</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.17382613793671</v>
+        <v>83.48358355485519</v>
       </c>
       <c r="C7" t="n">
-        <v>39.91281082359266</v>
+        <v>41.15339903560606</v>
       </c>
       <c r="D7" t="n">
-        <v>1.946640876975643</v>
+        <v>2.008656884920578</v>
       </c>
       <c r="E7" t="n">
-        <v>7.595262551004397</v>
+        <v>7.841095510664115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477335187901706</v>
+        <v>0.747888664028841</v>
       </c>
       <c r="G7" t="n">
-        <v>29.67402927278298</v>
+        <v>30.60834631633953</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39574186434784</v>
+        <v>34.40287854532668</v>
       </c>
       <c r="I7" t="n">
-        <v>3.141083561597116</v>
+        <v>3.200413483395199</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673334492438565</v>
+        <v>4.674304150180255</v>
       </c>
       <c r="K7" t="n">
-        <v>17.82617386206327</v>
+        <v>16.51641644514479</v>
       </c>
       <c r="L7" t="n">
-        <v>42.15644576752425</v>
+        <v>42.22364021865238</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8954304531802</v>
+        <v>99.89345569940323</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.27147429179823</v>
+        <v>88.29539698610434</v>
       </c>
       <c r="C8" t="n">
-        <v>42.22341710090976</v>
+        <v>43.40948519229557</v>
       </c>
       <c r="D8" t="n">
-        <v>1.950952490727708</v>
+        <v>2.012928673513284</v>
       </c>
       <c r="E8" t="n">
-        <v>9.444085191672432</v>
+        <v>9.642855152447048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749389673328292</v>
+        <v>0.7494791906576529</v>
       </c>
       <c r="G8" t="n">
-        <v>30.17251036728719</v>
+        <v>31.09654065229337</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47192497310142</v>
+        <v>34.47604277025202</v>
       </c>
       <c r="I8" t="n">
-        <v>5.798926137379368</v>
+        <v>5.633305605330617</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683685458301824</v>
+        <v>4.684244941610329</v>
       </c>
       <c r="K8" t="n">
-        <v>12.72852570820175</v>
+        <v>11.70460301389568</v>
       </c>
       <c r="L8" t="n">
-        <v>44.85518684140131</v>
+        <v>44.698533435799</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80712965051282</v>
+        <v>99.81262164199025</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.24321094589459</v>
+        <v>86.45118205068673</v>
       </c>
       <c r="C9" t="n">
-        <v>41.09408078508132</v>
+        <v>42.43999228978966</v>
       </c>
       <c r="D9" t="n">
-        <v>1.859270346664415</v>
+        <v>1.92958924409957</v>
       </c>
       <c r="E9" t="n">
-        <v>9.80720553182568</v>
+        <v>10.02744322544512</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750808451272253</v>
+        <v>0.7508382432415047</v>
       </c>
       <c r="G9" t="n">
-        <v>28.75459760139866</v>
+        <v>29.80907925894988</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53718875852363</v>
+        <v>34.53855918910921</v>
       </c>
       <c r="I9" t="n">
-        <v>4.841587435758369</v>
+        <v>4.702933869582028</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692552820451581</v>
+        <v>4.692739020259403</v>
       </c>
       <c r="K9" t="n">
-        <v>14.75678905410541</v>
+        <v>13.54881794931329</v>
       </c>
       <c r="L9" t="n">
-        <v>43.98804887921938</v>
+        <v>43.85470904963787</v>
       </c>
       <c r="M9" t="n">
-        <v>99.83891871840612</v>
+        <v>99.84351928874081</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.07118731840838</v>
+        <v>84.40286292010525</v>
       </c>
       <c r="C10" t="n">
-        <v>39.6723010030857</v>
+        <v>41.12181610081881</v>
       </c>
       <c r="D10" t="n">
-        <v>1.762215529543908</v>
+        <v>1.837801663669166</v>
       </c>
       <c r="E10" t="n">
-        <v>9.968797748707939</v>
+        <v>10.2046510507036</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520259476740864</v>
+        <v>0.7520021770710077</v>
       </c>
       <c r="G10" t="n">
-        <v>27.25359360992199</v>
+        <v>28.39110739348483</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59319359300797</v>
+        <v>34.59210014526634</v>
       </c>
       <c r="I10" t="n">
-        <v>4.041198716589458</v>
+        <v>3.925186883216516</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700162172963039</v>
+        <v>4.700013606693796</v>
       </c>
       <c r="K10" t="n">
-        <v>16.92881268159161</v>
+        <v>15.59713707989472</v>
       </c>
       <c r="L10" t="n">
-        <v>43.26439777544052</v>
+        <v>43.15040976735364</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86551146011783</v>
+        <v>99.86936294806718</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.78644794657056</v>
+        <v>82.13929916218072</v>
       </c>
       <c r="C11" t="n">
-        <v>38.01317106353639</v>
+        <v>39.46716337189523</v>
       </c>
       <c r="D11" t="n">
-        <v>1.661247146642864</v>
+        <v>1.737223313542111</v>
       </c>
       <c r="E11" t="n">
-        <v>9.959681385775818</v>
+        <v>10.1920651464729</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530723673679078</v>
+        <v>0.7530017231391753</v>
       </c>
       <c r="G11" t="n">
-        <v>25.69206425729607</v>
+        <v>26.83733214321344</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64132889892375</v>
+        <v>34.63807926440206</v>
       </c>
       <c r="I11" t="n">
-        <v>3.372351594514715</v>
+        <v>3.275336801791197</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706702296049423</v>
+        <v>4.706260769619844</v>
       </c>
       <c r="K11" t="n">
-        <v>19.21355205342945</v>
+        <v>17.86070083781928</v>
       </c>
       <c r="L11" t="n">
-        <v>42.66102136312889</v>
+        <v>42.56310282130723</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88774448009474</v>
+        <v>99.89096703102175</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.3827499052237</v>
+        <v>79.89625701357745</v>
       </c>
       <c r="C12" t="n">
-        <v>36.13074928164061</v>
+        <v>37.73148806690205</v>
       </c>
       <c r="D12" t="n">
-        <v>1.556089532622747</v>
+        <v>1.638573246469032</v>
       </c>
       <c r="E12" t="n">
-        <v>9.798172145820715</v>
+        <v>10.06872442941366</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539734526684941</v>
+        <v>0.7538601787300366</v>
       </c>
       <c r="G12" t="n">
-        <v>24.0657462335098</v>
+        <v>25.31334579364485</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68277882275073</v>
+        <v>34.67756822158168</v>
       </c>
       <c r="I12" t="n">
-        <v>2.813655638673128</v>
+        <v>2.732559026675486</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712334079178087</v>
+        <v>4.711626117062726</v>
       </c>
       <c r="K12" t="n">
-        <v>21.61725009477631</v>
+        <v>20.10374298642253</v>
       </c>
       <c r="L12" t="n">
-        <v>42.15832419040211</v>
+        <v>42.0737873688479</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90632356681903</v>
+        <v>99.90901842217248</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.97620129782348</v>
+        <v>77.54926782565263</v>
       </c>
       <c r="C13" t="n">
-        <v>34.15821826259283</v>
+        <v>35.807036547371</v>
       </c>
       <c r="D13" t="n">
-        <v>1.451857366536036</v>
+        <v>1.536196609899383</v>
       </c>
       <c r="E13" t="n">
-        <v>9.533045193591722</v>
+        <v>9.819533175158639</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547498676600944</v>
+        <v>0.7545987721659742</v>
       </c>
       <c r="G13" t="n">
-        <v>22.45374075064793</v>
+        <v>23.73178988318295</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71849391236434</v>
+        <v>34.71154351963481</v>
       </c>
       <c r="I13" t="n">
-        <v>2.347127534147772</v>
+        <v>2.279363539573546</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71718667287559</v>
+        <v>4.716242326037336</v>
       </c>
       <c r="K13" t="n">
-        <v>24.02379870217651</v>
+        <v>22.45073217434737</v>
       </c>
       <c r="L13" t="n">
-        <v>41.73982593415642</v>
+        <v>41.66632686087398</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92184289892576</v>
+        <v>99.92409558259234</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.95692857661464</v>
+        <v>84.09759178174791</v>
       </c>
       <c r="C14" t="n">
-        <v>38.43709485229972</v>
+        <v>39.7877731895235</v>
       </c>
       <c r="D14" t="n">
-        <v>1.453678745399451</v>
+        <v>1.538063506346016</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92969435520028</v>
+        <v>12.06219505625453</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556967137400238</v>
+        <v>0.7555158147875448</v>
       </c>
       <c r="G14" t="n">
-        <v>24.34624500346669</v>
+        <v>25.48035177158623</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62638449905352</v>
+        <v>36.47344879319901</v>
       </c>
       <c r="I14" t="n">
-        <v>3.122124798879538</v>
+        <v>3.066042997152429</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723104460875148</v>
+        <v>4.721973842422153</v>
       </c>
       <c r="K14" t="n">
-        <v>17.04307142338533</v>
+        <v>15.90240821825209</v>
       </c>
       <c r="L14" t="n">
-        <v>44.4158932926608</v>
+        <v>44.20774121075094</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89605956834586</v>
+        <v>99.89792261852652</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.33019065970055</v>
+        <v>83.42369070512176</v>
       </c>
       <c r="C15" t="n">
-        <v>38.29028111968083</v>
+        <v>39.58806437750825</v>
       </c>
       <c r="D15" t="n">
-        <v>1.430816045869858</v>
+        <v>1.513086055475144</v>
       </c>
       <c r="E15" t="n">
-        <v>12.1780823173833</v>
+        <v>12.29258499389547</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564935955116016</v>
+        <v>0.7562879146967511</v>
       </c>
       <c r="G15" t="n">
-        <v>23.96526624142744</v>
+        <v>25.06656246319849</v>
       </c>
       <c r="H15" t="n">
-        <v>36.66693325608299</v>
+        <v>36.51072285940712</v>
       </c>
       <c r="I15" t="n">
-        <v>2.604514231477846</v>
+        <v>2.55764695159409</v>
       </c>
       <c r="J15" t="n">
-        <v>4.728084971947509</v>
+        <v>4.726799466854692</v>
       </c>
       <c r="K15" t="n">
-        <v>17.66980934029945</v>
+        <v>16.57630929487823</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95318385116195</v>
+        <v>43.75045846658152</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91327431114223</v>
+        <v>99.91483213896799</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.87249327436612</v>
+        <v>81.1371904844539</v>
       </c>
       <c r="C16" t="n">
-        <v>36.23469890256303</v>
+        <v>37.69724994987494</v>
       </c>
       <c r="D16" t="n">
-        <v>1.338439805931199</v>
+        <v>1.425333011143664</v>
       </c>
       <c r="E16" t="n">
-        <v>11.75390790883281</v>
+        <v>11.93520344085662</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571794402412051</v>
+        <v>0.7569507196355302</v>
       </c>
       <c r="G16" t="n">
-        <v>22.41802249132953</v>
+        <v>23.61280035950894</v>
       </c>
       <c r="H16" t="n">
-        <v>36.7001758678825</v>
+        <v>36.54272057741814</v>
       </c>
       <c r="I16" t="n">
-        <v>2.172396258641342</v>
+        <v>2.133240378168952</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732371501507531</v>
+        <v>4.730941997722061</v>
       </c>
       <c r="K16" t="n">
-        <v>20.12750672563388</v>
+        <v>18.86280951554609</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56544675426204</v>
+        <v>43.36889478592356</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92765238245894</v>
+        <v>99.92895425134459</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.87745770588714</v>
+        <v>82.76664623657754</v>
       </c>
       <c r="C17" t="n">
-        <v>37.66513767901998</v>
+        <v>38.88238329823993</v>
       </c>
       <c r="D17" t="n">
-        <v>1.339634467040939</v>
+        <v>1.426563449246754</v>
       </c>
       <c r="E17" t="n">
-        <v>12.64652184428245</v>
+        <v>12.70067541422898</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578552814903539</v>
+        <v>0.7576041676370282</v>
       </c>
       <c r="G17" t="n">
-        <v>22.95474513652043</v>
+        <v>24.03110601321953</v>
       </c>
       <c r="H17" t="n">
-        <v>37.24964644026946</v>
+        <v>36.97218816057374</v>
       </c>
       <c r="I17" t="n">
-        <v>2.192459026968785</v>
+        <v>2.143482983940084</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736595509314711</v>
+        <v>4.735026047731424</v>
       </c>
       <c r="K17" t="n">
-        <v>18.12254229411287</v>
+        <v>17.23335376342245</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13930323244138</v>
+        <v>43.81287513203412</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92698320557423</v>
+        <v>99.92861219369649</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.53829653836347</v>
+        <v>80.65300233419644</v>
       </c>
       <c r="C18" t="n">
-        <v>35.66410376000063</v>
+        <v>37.10001111194284</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25576804592603</v>
+        <v>1.348539656256438</v>
       </c>
       <c r="E18" t="n">
-        <v>12.15954104611053</v>
+        <v>12.30395653354005</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584360079888748</v>
+        <v>0.7581638737978144</v>
       </c>
       <c r="G18" t="n">
-        <v>21.5176872154465</v>
+        <v>22.71675995879495</v>
       </c>
       <c r="H18" t="n">
-        <v>37.27818995943034</v>
+        <v>36.99950263741427</v>
       </c>
       <c r="I18" t="n">
-        <v>1.828449213530731</v>
+        <v>1.787555463156576</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740225049930467</v>
+        <v>4.738524211236337</v>
       </c>
       <c r="K18" t="n">
-        <v>20.46170346163653</v>
+        <v>19.34699766580358</v>
       </c>
       <c r="L18" t="n">
-        <v>43.81329113872482</v>
+        <v>43.49345002825523</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93909836036198</v>
+        <v>99.94045880600166</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.66184127539712</v>
+        <v>79.86963638854674</v>
       </c>
       <c r="C19" t="n">
-        <v>35.06892833216263</v>
+        <v>36.59232566884468</v>
       </c>
       <c r="D19" t="n">
-        <v>1.225052304938757</v>
+        <v>1.320313972746384</v>
       </c>
       <c r="E19" t="n">
-        <v>12.11623737323691</v>
+        <v>12.29485393060165</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589260301734633</v>
+        <v>0.7586355114683386</v>
       </c>
       <c r="G19" t="n">
-        <v>20.99137050488916</v>
+        <v>22.241285563959</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30227523477198</v>
+        <v>37.02251924350374</v>
       </c>
       <c r="I19" t="n">
-        <v>1.524692138802724</v>
+        <v>1.490556219590523</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743287688584145</v>
+        <v>4.741471946677113</v>
       </c>
       <c r="K19" t="n">
-        <v>21.33815872460287</v>
+        <v>20.13036361145323</v>
       </c>
       <c r="L19" t="n">
-        <v>43.54212268730308</v>
+        <v>43.2276564012811</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94920974406858</v>
+        <v>99.95034568157901</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.10369146496417</v>
+        <v>77.4954759153667</v>
       </c>
       <c r="C20" t="n">
-        <v>32.74519919986126</v>
+        <v>34.44795020276067</v>
       </c>
       <c r="D20" t="n">
-        <v>1.134404134951555</v>
+        <v>1.233551192357509</v>
       </c>
       <c r="E20" t="n">
-        <v>11.43157289957621</v>
+        <v>11.69404535515943</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593486162105237</v>
+        <v>0.7590410524758507</v>
       </c>
       <c r="G20" t="n">
-        <v>19.43810676739784</v>
+        <v>20.77972731737162</v>
       </c>
       <c r="H20" t="n">
-        <v>37.32304592919815</v>
+        <v>37.04231023605244</v>
       </c>
       <c r="I20" t="n">
-        <v>1.271284266314122</v>
+        <v>1.242794183975786</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745928851315773</v>
+        <v>4.744006577974064</v>
       </c>
       <c r="K20" t="n">
-        <v>23.89630853503583</v>
+        <v>22.5045240846333</v>
       </c>
       <c r="L20" t="n">
-        <v>43.31613970569173</v>
+        <v>43.00612137317295</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95764744058881</v>
+        <v>99.95859566056691</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.04674046253041</v>
+        <v>83.00985459535062</v>
       </c>
       <c r="C21" t="n">
-        <v>36.40173262147562</v>
+        <v>37.78972021725701</v>
       </c>
       <c r="D21" t="n">
-        <v>1.135257099271265</v>
+        <v>1.234475903543743</v>
       </c>
       <c r="E21" t="n">
-        <v>13.41491470647632</v>
+        <v>13.52130230210479</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599195743513599</v>
+        <v>0.7596100550080388</v>
       </c>
       <c r="G21" t="n">
-        <v>21.11901189187511</v>
+        <v>22.30266039341445</v>
       </c>
       <c r="H21" t="n">
-        <v>39.01739883167199</v>
+        <v>38.57743428757738</v>
       </c>
       <c r="I21" t="n">
-        <v>1.850741019188356</v>
+        <v>1.866808809901985</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749497339695998</v>
+        <v>4.74756284380024</v>
       </c>
       <c r="K21" t="n">
-        <v>17.95325953746959</v>
+        <v>16.99014540464939</v>
       </c>
       <c r="L21" t="n">
-        <v>45.58336282495405</v>
+        <v>45.1579540302297</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93835498389926</v>
+        <v>99.9378196521361</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_7_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.23535751270754</v>
+        <v>43.93649775846116</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7051283870477</v>
+        <v>94.16028025851716</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03369476865926</v>
+        <v>81.44295149316707</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89828209672594</v>
+        <v>43.19850704872264</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22877005237442</v>
+        <v>2.17861679714038</v>
       </c>
       <c r="E3" t="n">
-        <v>5.689460331748026</v>
+        <v>4.143256473290924</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429233507914735</v>
+        <v>0.7376090084020183</v>
       </c>
       <c r="G3" t="n">
-        <v>33.962478178676</v>
+        <v>32.77002765698656</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17447413640778</v>
+        <v>33.93001438649284</v>
       </c>
       <c r="I3" t="n">
-        <v>6.592317776214852</v>
+        <v>3.073370868341743</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643270942446709</v>
+        <v>4.610056302512614</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96630523134073</v>
+        <v>18.55704850683292</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89878645670967</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7633737847763</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.19414353015281</v>
+        <v>88.59431030812233</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69968036622443</v>
+        <v>42.84786103638519</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188688118425159</v>
+        <v>2.184348338688848</v>
       </c>
       <c r="E4" t="n">
-        <v>6.504668383707318</v>
+        <v>6.560143499536967</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444868777158694</v>
+        <v>0.7395495225317769</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35170103472584</v>
+        <v>33.4765445458826</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24639637492999</v>
+        <v>34.01927803646173</v>
       </c>
       <c r="I4" t="n">
-        <v>5.505159754924462</v>
+        <v>6.992261849196798</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653042985724183</v>
+        <v>4.622184515823606</v>
       </c>
       <c r="K4" t="n">
-        <v>12.80585646984717</v>
+        <v>11.40568969187769</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31134322570021</v>
+        <v>45.51398544648771</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81688006177181</v>
+        <v>99.76753617475057</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12163390237106</v>
+        <v>87.44206324215632</v>
       </c>
       <c r="C5" t="n">
-        <v>42.48164030830971</v>
+        <v>42.7794863197293</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136651723344799</v>
+        <v>2.129465709438811</v>
       </c>
       <c r="E5" t="n">
-        <v>7.115984498534558</v>
+        <v>7.368626688949852</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458111706100432</v>
+        <v>0.7411958938480689</v>
       </c>
       <c r="G5" t="n">
-        <v>32.55875923683559</v>
+        <v>32.63543291989221</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30731384806198</v>
+        <v>34.09501111701118</v>
       </c>
       <c r="I5" t="n">
-        <v>4.595793608671321</v>
+        <v>5.839856576465761</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661319816312769</v>
+        <v>4.632474336550431</v>
       </c>
       <c r="K5" t="n">
-        <v>13.87836609762894</v>
+        <v>12.55793675784369</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48707248975789</v>
+        <v>44.46834742661601</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84707889569654</v>
+        <v>99.805770504189</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.90920530396744</v>
+        <v>86.04370583688205</v>
       </c>
       <c r="C6" t="n">
-        <v>41.9830826987924</v>
+        <v>42.2874549980305</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077818027156258</v>
+        <v>2.062680258956677</v>
       </c>
       <c r="E6" t="n">
-        <v>7.559308368530477</v>
+        <v>7.950151080209637</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469341856602785</v>
+        <v>0.7425959102596273</v>
       </c>
       <c r="G6" t="n">
-        <v>31.66223870038749</v>
+        <v>31.6119028956361</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3589725403728</v>
+        <v>34.15941187194286</v>
       </c>
       <c r="I6" t="n">
-        <v>3.835594821483401</v>
+        <v>4.875739380754488</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668338660376739</v>
+        <v>4.641224439122672</v>
       </c>
       <c r="K6" t="n">
-        <v>15.09079469603254</v>
+        <v>13.95629416311793</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79846167160085</v>
+        <v>43.59403260061641</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87233906642579</v>
+        <v>99.83778176176484</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.48358355485519</v>
+        <v>84.48324969166451</v>
       </c>
       <c r="C7" t="n">
-        <v>41.15339903560606</v>
+        <v>41.48406002494927</v>
       </c>
       <c r="D7" t="n">
-        <v>2.008656884920578</v>
+        <v>1.988540988190945</v>
       </c>
       <c r="E7" t="n">
-        <v>7.841095510664115</v>
+        <v>8.342670816760634</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747888664028841</v>
+        <v>0.7437882958305216</v>
       </c>
       <c r="G7" t="n">
-        <v>30.60834631633953</v>
+        <v>30.47567084123856</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40287854532668</v>
+        <v>34.214261608204</v>
       </c>
       <c r="I7" t="n">
-        <v>3.200413483395199</v>
+        <v>4.069640292499091</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674304150180255</v>
+        <v>4.64867684894076</v>
       </c>
       <c r="K7" t="n">
-        <v>16.51641644514479</v>
+        <v>15.51675030833549</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22364021865238</v>
+        <v>42.86375246169428</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89345569940323</v>
+        <v>99.86456279497902</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.29539698610434</v>
+        <v>82.74557951539086</v>
       </c>
       <c r="C8" t="n">
-        <v>43.40948519229557</v>
+        <v>40.37822858414964</v>
       </c>
       <c r="D8" t="n">
-        <v>2.012928673513284</v>
+        <v>1.906467984067278</v>
       </c>
       <c r="E8" t="n">
-        <v>9.642855152447048</v>
+        <v>8.564345045040939</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494791906576529</v>
+        <v>0.7448058365392488</v>
       </c>
       <c r="G8" t="n">
-        <v>31.09654065229337</v>
+        <v>29.21784921549478</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47604277025202</v>
+        <v>34.26106848080545</v>
       </c>
       <c r="I8" t="n">
-        <v>5.633305605330617</v>
+        <v>3.396006475072846</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684244941610329</v>
+        <v>4.655036478370305</v>
       </c>
       <c r="K8" t="n">
-        <v>11.70460301389568</v>
+        <v>17.25442048460916</v>
       </c>
       <c r="L8" t="n">
-        <v>44.698533435799</v>
+        <v>42.25430536756067</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81262164199025</v>
+        <v>99.88695443631947</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.45118205068673</v>
+        <v>80.87269538156828</v>
       </c>
       <c r="C9" t="n">
-        <v>42.43999228978966</v>
+        <v>39.03225151330201</v>
       </c>
       <c r="D9" t="n">
-        <v>1.92958924409957</v>
+        <v>1.818624229232602</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02744322544512</v>
+        <v>8.641946663617947</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508382432415047</v>
+        <v>0.7456756257945009</v>
       </c>
       <c r="G9" t="n">
-        <v>29.80907925894988</v>
+        <v>27.8715871199694</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53855918910921</v>
+        <v>34.30107878654704</v>
       </c>
       <c r="I9" t="n">
-        <v>4.702933869582028</v>
+        <v>2.833310295191138</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692739020259403</v>
+        <v>4.66047266121563</v>
       </c>
       <c r="K9" t="n">
-        <v>13.54881794931329</v>
+        <v>19.12730461843174</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85470904963787</v>
+        <v>41.7461103550698</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84351928874081</v>
+        <v>99.90566648680354</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.40286292010525</v>
+        <v>85.8049393967265</v>
       </c>
       <c r="C10" t="n">
-        <v>41.12181610081881</v>
+        <v>42.3758692793368</v>
       </c>
       <c r="D10" t="n">
-        <v>1.837801663669166</v>
+        <v>1.820722709211858</v>
       </c>
       <c r="E10" t="n">
-        <v>10.2046510507036</v>
+        <v>10.55036125433293</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520021770710077</v>
+        <v>0.7465360483857083</v>
       </c>
       <c r="G10" t="n">
-        <v>28.39110739348483</v>
+        <v>29.30714607184609</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59210014526634</v>
+        <v>35.74405662096265</v>
       </c>
       <c r="I10" t="n">
-        <v>3.925186883216516</v>
+        <v>2.97026638957658</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700013606693796</v>
+        <v>4.665850302410677</v>
       </c>
       <c r="K10" t="n">
-        <v>15.59713707989472</v>
+        <v>14.1950606032735</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15040976735364</v>
+        <v>43.3301753507488</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86936294806718</v>
+        <v>99.90110523335909</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.13929916218072</v>
+        <v>85.51428317140719</v>
       </c>
       <c r="C11" t="n">
-        <v>39.46716337189523</v>
+        <v>42.44745761395718</v>
       </c>
       <c r="D11" t="n">
-        <v>1.737223313542111</v>
+        <v>1.800510440033395</v>
       </c>
       <c r="E11" t="n">
-        <v>10.1920651464729</v>
+        <v>10.90663180352134</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530017231391753</v>
+        <v>0.7472700828386055</v>
       </c>
       <c r="G11" t="n">
-        <v>26.83733214321344</v>
+        <v>29.0347819142062</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63807926440206</v>
+        <v>35.83218343684665</v>
       </c>
       <c r="I11" t="n">
-        <v>3.275336801791197</v>
+        <v>2.522467476219723</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706260769619844</v>
+        <v>4.670438017741285</v>
       </c>
       <c r="K11" t="n">
-        <v>17.86070083781928</v>
+        <v>14.48571682859281</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56310282130723</v>
+        <v>42.98282590122909</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89096703102175</v>
+        <v>99.91600034377907</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.89625701357745</v>
+        <v>83.54038123724855</v>
       </c>
       <c r="C12" t="n">
-        <v>37.73148806690205</v>
+        <v>40.86563501147142</v>
       </c>
       <c r="D12" t="n">
-        <v>1.638573246469032</v>
+        <v>1.716807431200642</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06872442941366</v>
+        <v>10.75023577431129</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538601787300366</v>
+        <v>0.7478973732218649</v>
       </c>
       <c r="G12" t="n">
-        <v>25.31334579364485</v>
+        <v>27.68499878994019</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67756822158168</v>
+        <v>35.8622625000894</v>
       </c>
       <c r="I12" t="n">
-        <v>2.732559026675486</v>
+        <v>2.103820785848512</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711626117062726</v>
+        <v>4.674358582636656</v>
       </c>
       <c r="K12" t="n">
-        <v>20.10374298642253</v>
+        <v>16.45961876275145</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0737873688479</v>
+        <v>42.60467768477103</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90901842217248</v>
+        <v>99.92993145899391</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.54926782565263</v>
+        <v>84.73423553299789</v>
       </c>
       <c r="C13" t="n">
-        <v>35.807036547371</v>
+        <v>41.8589127427044</v>
       </c>
       <c r="D13" t="n">
-        <v>1.536196609899383</v>
+        <v>1.71813019382097</v>
       </c>
       <c r="E13" t="n">
-        <v>9.819533175158639</v>
+        <v>11.40158941058881</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545987721659742</v>
+        <v>0.7484736118093503</v>
       </c>
       <c r="G13" t="n">
-        <v>23.73178988318295</v>
+        <v>28.02297090430282</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71154351963481</v>
+        <v>36.20653501750002</v>
       </c>
       <c r="I13" t="n">
-        <v>2.279363539573546</v>
+        <v>1.958576321167481</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716242326037336</v>
+        <v>4.67796007380844</v>
       </c>
       <c r="K13" t="n">
-        <v>22.45073217434737</v>
+        <v>15.26576446700212</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66632686087398</v>
+        <v>42.81008717553727</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92409558259234</v>
+        <v>99.93476438524378</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.09759178174791</v>
+        <v>82.80162590727986</v>
       </c>
       <c r="C14" t="n">
-        <v>39.7877731895235</v>
+        <v>40.23057898385498</v>
       </c>
       <c r="D14" t="n">
-        <v>1.538063506346016</v>
+        <v>1.638500457058107</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06219505625453</v>
+        <v>11.14536622868536</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555158147875448</v>
+        <v>0.7489657205456602</v>
       </c>
       <c r="G14" t="n">
-        <v>25.48035177158623</v>
+        <v>26.72419750258497</v>
       </c>
       <c r="H14" t="n">
-        <v>36.47344879319901</v>
+        <v>36.23034020169422</v>
       </c>
       <c r="I14" t="n">
-        <v>3.066042997152429</v>
+        <v>1.633220043301181</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721973842422153</v>
+        <v>4.681035753410376</v>
       </c>
       <c r="K14" t="n">
-        <v>15.90240821825209</v>
+        <v>17.19837409272013</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20774121075094</v>
+        <v>42.51664202561469</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89792261852652</v>
+        <v>99.9455951021898</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.42369070512176</v>
+        <v>81.95471143273431</v>
       </c>
       <c r="C15" t="n">
-        <v>39.58806437750825</v>
+        <v>39.6130269053166</v>
       </c>
       <c r="D15" t="n">
-        <v>1.513086055475144</v>
+        <v>1.603127027675143</v>
       </c>
       <c r="E15" t="n">
-        <v>12.29258499389547</v>
+        <v>11.13557486616559</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562879146967511</v>
+        <v>0.7493876119059305</v>
       </c>
       <c r="G15" t="n">
-        <v>25.06656246319849</v>
+        <v>26.1472513631427</v>
       </c>
       <c r="H15" t="n">
-        <v>36.51072285940712</v>
+        <v>36.25074870249932</v>
       </c>
       <c r="I15" t="n">
-        <v>2.55764695159409</v>
+        <v>1.384949286933567</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726799466854692</v>
+        <v>4.683672574412065</v>
       </c>
       <c r="K15" t="n">
-        <v>16.57630929487823</v>
+        <v>18.04528856726569</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75045846658152</v>
+        <v>42.29554554121407</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91483213896799</v>
+        <v>99.95386101379636</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.1371904844539</v>
+        <v>79.66327302111409</v>
       </c>
       <c r="C16" t="n">
-        <v>37.69724994987494</v>
+        <v>37.5362565248988</v>
       </c>
       <c r="D16" t="n">
-        <v>1.425333011143664</v>
+        <v>1.509388230848793</v>
       </c>
       <c r="E16" t="n">
-        <v>11.93520344085662</v>
+        <v>10.6768973040146</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569507196355302</v>
+        <v>0.7497496793808502</v>
       </c>
       <c r="G16" t="n">
-        <v>23.61280035950894</v>
+        <v>24.61835699558181</v>
       </c>
       <c r="H16" t="n">
-        <v>36.54272057741814</v>
+        <v>36.26826329286368</v>
       </c>
       <c r="I16" t="n">
-        <v>2.133240378168952</v>
+        <v>1.154682022294051</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730941997722061</v>
+        <v>4.685935496130313</v>
       </c>
       <c r="K16" t="n">
-        <v>18.86280951554609</v>
+        <v>20.33672697888591</v>
       </c>
       <c r="L16" t="n">
-        <v>43.36889478592356</v>
+        <v>42.08854568268935</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92895425134459</v>
+        <v>99.96152918647405</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.76664623657754</v>
+        <v>84.43488102301895</v>
       </c>
       <c r="C17" t="n">
-        <v>38.88238329823993</v>
+        <v>40.66105502321408</v>
       </c>
       <c r="D17" t="n">
-        <v>1.426563449246754</v>
+        <v>1.51018292124857</v>
       </c>
       <c r="E17" t="n">
-        <v>12.70067541422898</v>
+        <v>12.34780496783361</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576041676370282</v>
+        <v>0.7501444213433636</v>
       </c>
       <c r="G17" t="n">
-        <v>24.03110601321953</v>
+        <v>26.07433069080992</v>
       </c>
       <c r="H17" t="n">
-        <v>36.97218816057374</v>
+        <v>37.7303706444325</v>
       </c>
       <c r="I17" t="n">
-        <v>2.143482983940084</v>
+        <v>1.333644743954964</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735026047731424</v>
+        <v>4.688402633396022</v>
       </c>
       <c r="K17" t="n">
-        <v>17.23335376342245</v>
+        <v>15.56511897698106</v>
       </c>
       <c r="L17" t="n">
-        <v>43.81287513203412</v>
+        <v>43.72939456808147</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92861219369649</v>
+        <v>99.9555685682766</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.65300233419644</v>
+        <v>86.10215369671018</v>
       </c>
       <c r="C18" t="n">
-        <v>37.10001111194284</v>
+        <v>41.41234236129634</v>
       </c>
       <c r="D18" t="n">
-        <v>1.348539656256438</v>
+        <v>1.511468941865701</v>
       </c>
       <c r="E18" t="n">
-        <v>12.30395653354005</v>
+        <v>12.96752333617144</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581638737978144</v>
+        <v>0.7507832189208624</v>
       </c>
       <c r="G18" t="n">
-        <v>22.71675995879495</v>
+        <v>26.21783221221838</v>
       </c>
       <c r="H18" t="n">
-        <v>36.99950263741427</v>
+        <v>37.76250054992808</v>
       </c>
       <c r="I18" t="n">
-        <v>1.787555463156576</v>
+        <v>2.199650319350322</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738524211236337</v>
+        <v>4.69239511825539</v>
       </c>
       <c r="K18" t="n">
-        <v>19.34699766580358</v>
+        <v>13.89784630328982</v>
       </c>
       <c r="L18" t="n">
-        <v>43.49345002825523</v>
+        <v>44.61655204323366</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94045880600166</v>
+        <v>99.92674070781983</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.86963638854674</v>
+        <v>83.49820535587409</v>
       </c>
       <c r="C19" t="n">
-        <v>36.59232566884468</v>
+        <v>39.14916635713897</v>
       </c>
       <c r="D19" t="n">
-        <v>1.320313972746384</v>
+        <v>1.415795046888437</v>
       </c>
       <c r="E19" t="n">
-        <v>12.29485393060165</v>
+        <v>12.45242774481787</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586355114683386</v>
+        <v>0.7513330211301246</v>
       </c>
       <c r="G19" t="n">
-        <v>22.241285563959</v>
+        <v>24.55827966957264</v>
       </c>
       <c r="H19" t="n">
-        <v>37.02251924350374</v>
+        <v>37.79015421307129</v>
       </c>
       <c r="I19" t="n">
-        <v>1.490556219590523</v>
+        <v>1.834384278330462</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741471946677113</v>
+        <v>4.695831382063278</v>
       </c>
       <c r="K19" t="n">
-        <v>20.13036361145323</v>
+        <v>16.50179464412589</v>
       </c>
       <c r="L19" t="n">
-        <v>43.2276564012811</v>
+        <v>44.2879376009754</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95034568157901</v>
+        <v>99.93889860224027</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.4954759153667</v>
+        <v>80.83930859603136</v>
       </c>
       <c r="C20" t="n">
-        <v>34.44795020276067</v>
+        <v>36.77371431677887</v>
       </c>
       <c r="D20" t="n">
-        <v>1.233551192357509</v>
+        <v>1.318661219062237</v>
       </c>
       <c r="E20" t="n">
-        <v>11.69404535515943</v>
+        <v>11.85303700547369</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590410524758507</v>
+        <v>0.7518069045766143</v>
       </c>
       <c r="G20" t="n">
-        <v>20.77972731737162</v>
+        <v>22.87340323609835</v>
       </c>
       <c r="H20" t="n">
-        <v>37.04231023605244</v>
+        <v>37.81398935410493</v>
       </c>
       <c r="I20" t="n">
-        <v>1.242794183975786</v>
+        <v>1.529617723111695</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744006577974064</v>
+        <v>4.698793153603839</v>
       </c>
       <c r="K20" t="n">
-        <v>22.5045240846333</v>
+        <v>19.16069140396866</v>
       </c>
       <c r="L20" t="n">
-        <v>43.00612137317295</v>
+        <v>44.01463916040995</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95859566056691</v>
+        <v>99.94904488115748</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.00985459535062</v>
+        <v>78.05539608352979</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78972021725701</v>
+        <v>34.22544275869707</v>
       </c>
       <c r="D21" t="n">
-        <v>1.234475903543743</v>
+        <v>1.217478283353715</v>
       </c>
       <c r="E21" t="n">
-        <v>13.52130230210479</v>
+        <v>11.15609757026365</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596100550080388</v>
+        <v>0.7522163728493114</v>
       </c>
       <c r="G21" t="n">
-        <v>22.30266039341445</v>
+        <v>21.11829126676394</v>
       </c>
       <c r="H21" t="n">
-        <v>38.57743428757738</v>
+        <v>37.83458457451373</v>
       </c>
       <c r="I21" t="n">
-        <v>1.866808809901985</v>
+        <v>1.275375685477236</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74756284380024</v>
+        <v>4.701352330308196</v>
       </c>
       <c r="K21" t="n">
-        <v>16.99014540464939</v>
+        <v>21.94460391647021</v>
       </c>
       <c r="L21" t="n">
-        <v>45.1579540302297</v>
+        <v>43.78746394363518</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9378196521361</v>
+        <v>99.95751061880247</v>
       </c>
     </row>
   </sheetData>
